--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,137 +1056,137 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,164 +1231,164 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,287 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Ness Digital Engineering</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>FujiFilm</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>TECKpert</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Elm &amp; Oak Health</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Database Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Redapt inc</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Law School Admission Council</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Newtown, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SR Azure Data Factory- Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8625d99e5c7e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5d92a233a5130</t>
         </is>
       </c>
     </row>
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,94 +531,94 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5d92a233a5130</t>
+          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Java AWS Developer</t>
+          <t>Power BI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfc6ba885136236</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Java AWS Developer</t>
+          <t>Senior Data Engineer, Databricks</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Colas USA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
+          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Databricks</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Colas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
+          <t>https://www.indeed.com/viewjob?jk=623e6ba410872463</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Power BI Engineer</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,107 +653,107 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfc6ba885136236</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Colas USA</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Colas</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623e6ba410872463</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (On-Site)</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,186 +762,186 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,119 +951,119 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,425 +1231,75 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Merrimack, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Ness Digital Engineering</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>TECKpert</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Law School Admission Council</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Newtown, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Database Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Redapt inc</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (On-Site)</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,291 +657,291 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
+          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>Sr. Associate Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1055,251 +1055,6 @@
         </is>
       </c>
       <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Ness Digital Engineering</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>TECKpert</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Law School Admission Council</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Newtown, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Database Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Redapt inc</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,50 +1011,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,52 +783,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,50 +976,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,85 +906,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Database Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Redapt inc</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,42 +643,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Sr. Associate Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Associate Software Development Engineer - US Federal</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,180 +741,110 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Database Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Redapt inc</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Senior AI/ML Platform Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer, GovCloud</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
+          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Senior AI/ML Platform Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfc6ba885136236</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power BI Engineer</t>
+          <t>Senior Data Engineer, Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colas USA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfc6ba885136236</t>
+          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Colas USA</t>
+          <t>Colas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
+          <t>https://www.indeed.com/viewjob?jk=623e6ba410872463</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colas</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623e6ba410872463</t>
+          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Sr. Associate Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Associate Software Development Engineer - US Federal</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
+          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
+          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer, GovCloud</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
+          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Senior AI/ML Platform Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,40 +811,110 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Senior Engineer, IT Data</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Backend Engineer - AI Gateway</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cinter Networks</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Senior Database Engineer</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Redapt inc</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D14" t="n">
         <v>10.4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,41 +885,6 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Database Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Redapt inc</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power BI Engineer</t>
+          <t>Senior Data Engineer, Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colas USA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfc6ba885136236</t>
+          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Colas USA</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
+          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>Sr. Associate Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Colas</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623e6ba410872463</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
+          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Associate Software Development Engineer - US Federal</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
+          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>RoadSync</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
+          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior AI/ML Platform Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer, GovCloud</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,75 +811,40 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Backend Engineer - AI Gateway</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Cinter Networks</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Databricks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Colas USA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5d92a233a5130</t>
+          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Colas USA</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
+          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Sr. Associate Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Associate Software Development Engineer - US Federal</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
+          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
+          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
         </is>
       </c>
     </row>
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
+          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>RoadSync</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
+          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior AI/ML Platform Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RoadSync</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer, GovCloud</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,75 +776,40 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Backend Engineer - AI Gateway</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Cinter Networks</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -815,6 +815,41 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr Associate Data Analytics</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/job_matches_2026-08-16.xlsx
+++ b/results/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Colas USA</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
+          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Sr. Associate Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Associate Software Development Engineer - US Federal</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
+          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
+          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
         </is>
       </c>
     </row>
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
+          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>RoadSync</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
+          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior AI/ML Platform Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RoadSync</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer, GovCloud</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>
       </c>
     </row>
@@ -812,41 +812,6 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr Associate Data Analytics</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>
       </c>
     </row>
